--- a/RV32I_Decodings.xlsx
+++ b/RV32I_Decodings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\arinb\AICE2008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AF2006-21E3-45F1-9454-C4D037D4D9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5814DD-2855-4F54-A51A-595B24E025BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="181">
   <si>
     <t>Instruction</t>
   </si>
@@ -440,9 +440,6 @@
     <t>rd = PC + 4; PC += imm</t>
   </si>
   <si>
-    <t>BRANCH_OFF</t>
-  </si>
-  <si>
     <t>jalr</t>
   </si>
   <si>
@@ -491,9 +488,6 @@
     <t>ALU_MEMWRITE</t>
   </si>
   <si>
-    <t>PC_RD_ALU_PC</t>
-  </si>
-  <si>
     <t>zero</t>
   </si>
   <si>
@@ -558,6 +552,30 @@
   </si>
   <si>
     <t>imm[4:1]</t>
+  </si>
+  <si>
+    <t>PC_RD</t>
+  </si>
+  <si>
+    <t>Memory Access Size</t>
+  </si>
+  <si>
+    <t>MEMSIZE_NONE</t>
+  </si>
+  <si>
+    <t>MEMSIZE_S8</t>
+  </si>
+  <si>
+    <t>MEMSIZE_S16</t>
+  </si>
+  <si>
+    <t>MEMSIZE_S32</t>
+  </si>
+  <si>
+    <t>MEMSIZE_U8</t>
+  </si>
+  <si>
+    <t>MEMSIZE_U16</t>
   </si>
 </sst>
 </file>
@@ -604,7 +622,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -795,11 +813,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -929,7 +999,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1237,7 +1316,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AV45"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.59765625" style="36" bestFit="1" customWidth="1"/>
@@ -1254,14 +1333,14 @@
     <col min="12" max="12" width="11.3984375" style="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.59765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="48" width="3.3984375" style="8" customWidth="1"/>
-    <col min="49" max="52" width="7.46484375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="15.46484375" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="49" width="3.3984375" style="8" customWidth="1"/>
+    <col min="50" max="52" width="7.46484375" style="8" customWidth="1"/>
     <col min="53" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1372,7 @@
         <v>7</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>8</v>
@@ -1302,13 +1381,16 @@
         <v>9</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="O1" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -1338,10 +1420,10 @@
         <v>16</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>17</v>
@@ -1350,13 +1432,16 @@
         <v>18</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O2" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P2" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="18" t="s">
         <v>20</v>
       </c>
@@ -1386,10 +1471,10 @@
         <v>16</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L3" s="16" t="s">
         <v>23</v>
@@ -1398,13 +1483,16 @@
         <v>18</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O3" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P3" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="18" t="s">
         <v>24</v>
       </c>
@@ -1434,10 +1522,10 @@
         <v>16</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L4" s="16" t="s">
         <v>27</v>
@@ -1446,13 +1534,16 @@
         <v>18</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O4" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P4" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="18" t="s">
         <v>28</v>
       </c>
@@ -1482,10 +1573,10 @@
         <v>16</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L5" s="16" t="s">
         <v>31</v>
@@ -1494,13 +1585,16 @@
         <v>18</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O5" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P5" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="18" t="s">
         <v>32</v>
       </c>
@@ -1530,10 +1624,10 @@
         <v>16</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L6" s="16" t="s">
         <v>35</v>
@@ -1542,13 +1636,16 @@
         <v>18</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O6" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P6" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="18" t="s">
         <v>36</v>
       </c>
@@ -1578,10 +1675,10 @@
         <v>16</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>39</v>
@@ -1590,13 +1687,16 @@
         <v>18</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O7" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P7" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="18" t="s">
         <v>40</v>
       </c>
@@ -1626,10 +1726,10 @@
         <v>16</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>43</v>
@@ -1638,13 +1738,16 @@
         <v>18</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O8" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P8" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="18" t="s">
         <v>44</v>
       </c>
@@ -1674,10 +1777,10 @@
         <v>16</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>47</v>
@@ -1686,13 +1789,16 @@
         <v>18</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O9" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P9" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="18" t="s">
         <v>48</v>
       </c>
@@ -1722,10 +1828,10 @@
         <v>16</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>51</v>
@@ -1734,13 +1840,16 @@
         <v>18</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O10" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P10" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
         <v>52</v>
       </c>
@@ -1770,10 +1879,10 @@
         <v>16</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K11" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L11" s="26" t="s">
         <v>54</v>
@@ -1782,13 +1891,16 @@
         <v>18</v>
       </c>
       <c r="N11" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="O11" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="O11" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="P11" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
         <v>55</v>
       </c>
@@ -1815,13 +1927,13 @@
         <v>15</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>17</v>
@@ -1830,13 +1942,16 @@
         <v>18</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P12" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="18" t="s">
         <v>59</v>
       </c>
@@ -1863,13 +1978,13 @@
         <v>15</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>27</v>
@@ -1878,13 +1993,16 @@
         <v>18</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O13" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P13" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="18" t="s">
         <v>62</v>
       </c>
@@ -1911,13 +2029,13 @@
         <v>15</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>31</v>
@@ -1926,13 +2044,16 @@
         <v>18</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O14" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P14" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="18" t="s">
         <v>65</v>
       </c>
@@ -1959,13 +2080,13 @@
         <v>15</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J15" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>35</v>
@@ -1974,13 +2095,16 @@
         <v>18</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O15" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P15" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="18" t="s">
         <v>68</v>
       </c>
@@ -2007,13 +2131,13 @@
         <v>15</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L16" s="16" t="s">
         <v>71</v>
@@ -2022,13 +2146,16 @@
         <v>18</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O16" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P16" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="18" t="s">
         <v>72</v>
       </c>
@@ -2055,13 +2182,13 @@
         <v>15</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>75</v>
@@ -2070,13 +2197,16 @@
         <v>18</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O17" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O17" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P17" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="18" t="s">
         <v>76</v>
       </c>
@@ -2103,13 +2233,13 @@
         <v>15</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>75</v>
@@ -2118,13 +2248,16 @@
         <v>18</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O18" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P18" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="18" t="s">
         <v>79</v>
       </c>
@@ -2151,13 +2284,13 @@
         <v>15</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>51</v>
@@ -2166,13 +2299,16 @@
         <v>18</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O19" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O19" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P19" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24" t="s">
         <v>82</v>
       </c>
@@ -2199,13 +2335,13 @@
         <v>15</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J20" s="26" t="s">
         <v>7</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L20" s="26" t="s">
         <v>54</v>
@@ -2214,13 +2350,16 @@
         <v>18</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O20" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="O20" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="P20" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
         <v>84</v>
       </c>
@@ -2238,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>86</v>
@@ -2247,13 +2386,13 @@
         <v>15</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L21" s="11" t="s">
         <v>17</v>
@@ -2262,13 +2401,16 @@
         <v>87</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="O21" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="O21" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P21" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="18" t="s">
         <v>88</v>
       </c>
@@ -2286,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G22" s="19" t="s">
         <v>90</v>
@@ -2295,13 +2437,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>17</v>
@@ -2310,13 +2452,16 @@
         <v>87</v>
       </c>
       <c r="N22" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="O22" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="O22" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="P22" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="18" t="s">
         <v>91</v>
       </c>
@@ -2334,7 +2479,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G23" s="19" t="s">
         <v>93</v>
@@ -2343,13 +2488,13 @@
         <v>15</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>17</v>
@@ -2358,13 +2503,16 @@
         <v>87</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="O23" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="O23" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P23" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="18" t="s">
         <v>94</v>
       </c>
@@ -2382,7 +2530,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G24" s="19" t="s">
         <v>96</v>
@@ -2391,13 +2539,13 @@
         <v>15</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L24" s="16" t="s">
         <v>17</v>
@@ -2406,13 +2554,16 @@
         <v>87</v>
       </c>
       <c r="N24" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="O24" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="O24" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P24" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24" t="s">
         <v>97</v>
       </c>
@@ -2430,7 +2581,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G25" s="25" t="s">
         <v>99</v>
@@ -2439,13 +2590,13 @@
         <v>15</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J25" s="26" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L25" s="26" t="s">
         <v>17</v>
@@ -2454,13 +2605,16 @@
         <v>87</v>
       </c>
       <c r="N25" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="O25" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="O25" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="P25" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
         <v>100</v>
       </c>
@@ -2478,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>103</v>
@@ -2487,13 +2641,13 @@
         <v>15</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J26" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L26" s="11" t="s">
         <v>17</v>
@@ -2502,13 +2656,16 @@
         <v>104</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="O26" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="O26" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P26" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="18" t="s">
         <v>105</v>
       </c>
@@ -2526,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G27" s="19" t="s">
         <v>107</v>
@@ -2535,13 +2692,13 @@
         <v>15</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L27" s="16" t="s">
         <v>17</v>
@@ -2550,13 +2707,16 @@
         <v>104</v>
       </c>
       <c r="N27" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="O27" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="O27" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="P27" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="24" t="s">
         <v>108</v>
       </c>
@@ -2574,7 +2734,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G28" s="25" t="s">
         <v>110</v>
@@ -2583,13 +2743,13 @@
         <v>15</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J28" s="26" t="s">
         <v>7</v>
       </c>
       <c r="K28" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L28" s="26" t="s">
         <v>17</v>
@@ -2598,13 +2758,16 @@
         <v>104</v>
       </c>
       <c r="N28" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="O28" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="O28" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="P28" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
         <v>111</v>
       </c>
@@ -2622,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>114</v>
@@ -2637,7 +2800,7 @@
         <v>7</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L29" s="11" t="s">
         <v>27</v>
@@ -2646,13 +2809,16 @@
         <v>18</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="O29" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O29" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P29" s="17" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="18" t="s">
         <v>116</v>
       </c>
@@ -2670,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G30" s="19" t="s">
         <v>118</v>
@@ -2685,7 +2851,7 @@
         <v>7</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L30" s="16" t="s">
         <v>27</v>
@@ -2694,13 +2860,16 @@
         <v>18</v>
       </c>
       <c r="N30" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O30" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O30" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P30" s="23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="18" t="s">
         <v>120</v>
       </c>
@@ -2718,7 +2887,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G31" s="19" t="s">
         <v>122</v>
@@ -2733,7 +2902,7 @@
         <v>7</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L31" s="16" t="s">
         <v>51</v>
@@ -2742,13 +2911,16 @@
         <v>18</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O31" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O31" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P31" s="23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="18" t="s">
         <v>123</v>
       </c>
@@ -2766,7 +2938,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G32" s="19" t="s">
         <v>125</v>
@@ -2781,7 +2953,7 @@
         <v>7</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>51</v>
@@ -2790,13 +2962,16 @@
         <v>18</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O32" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O32" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P32" s="23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:48" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:49" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="18" t="s">
         <v>127</v>
       </c>
@@ -2814,7 +2989,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G33" s="19" t="s">
         <v>122</v>
@@ -2829,7 +3004,7 @@
         <v>7</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>54</v>
@@ -2838,13 +3013,16 @@
         <v>18</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O33" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="O33" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P33" s="23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="34" spans="1:48" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:49" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="24" t="s">
         <v>129</v>
       </c>
@@ -2862,7 +3040,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G34" s="25" t="s">
         <v>125</v>
@@ -2877,7 +3055,7 @@
         <v>7</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L34" s="26" t="s">
         <v>54</v>
@@ -2886,13 +3064,16 @@
         <v>18</v>
       </c>
       <c r="N34" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="O34" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="O34" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="P34" s="30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:48" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:49" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="18" t="s">
         <v>131</v>
       </c>
@@ -2907,19 +3088,19 @@
         <v>1101111</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G35" s="19" t="s">
         <v>134</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J35" s="15" t="s">
         <v>7</v>
@@ -2934,18 +3115,21 @@
         <v>18</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="O35" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="O35" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P35" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:49" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="18" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:48" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="18" t="s">
+      <c r="B36" s="19" t="s">
         <v>136</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>137</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>57</v>
@@ -2958,22 +3142,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H36" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J36" s="26" t="s">
         <v>7</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>17</v>
@@ -2982,46 +3166,49 @@
         <v>18</v>
       </c>
       <c r="N36" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="O36" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="O36" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="P36" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:49" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="9" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="37" spans="1:48" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="C37" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="D37" s="11" t="str">
         <f>HEX2BIN(37,7)</f>
         <v>0110111</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="J37" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="H37" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="I37" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="J37" s="16" t="s">
-        <v>144</v>
-      </c>
       <c r="K37" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L37" s="11" t="s">
         <v>17</v>
@@ -3030,46 +3217,49 @@
         <v>18</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="O37" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O37" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P37" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:48" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:49" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B38" s="25" t="s">
-        <v>146</v>
-      </c>
       <c r="C38" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D38" s="26" t="str">
         <f>HEX2BIN(17,7)</f>
         <v>0010111</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J38" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L38" s="26" t="s">
         <v>17</v>
@@ -3078,239 +3268,242 @@
         <v>18</v>
       </c>
       <c r="N38" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="O38" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="O38" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="P38" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:48" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="P39" s="45" t="s">
+    <row r="39" spans="1:49" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Q39" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="R39" s="45">
+        <v>31</v>
+      </c>
+      <c r="S39" s="45">
+        <v>30</v>
+      </c>
+      <c r="T39" s="45">
+        <v>29</v>
+      </c>
+      <c r="U39" s="45">
+        <f>T39-1</f>
+        <v>28</v>
+      </c>
+      <c r="V39" s="45">
+        <f>U39-1</f>
+        <v>27</v>
+      </c>
+      <c r="W39" s="45">
+        <f>V39-1</f>
+        <v>26</v>
+      </c>
+      <c r="X39" s="45">
+        <f>W39-1</f>
+        <v>25</v>
+      </c>
+      <c r="Y39" s="45">
+        <f>X39-1</f>
+        <v>24</v>
+      </c>
+      <c r="Z39" s="45">
+        <f>Y39-1</f>
+        <v>23</v>
+      </c>
+      <c r="AA39" s="45">
+        <f>Z39-1</f>
+        <v>22</v>
+      </c>
+      <c r="AB39" s="45">
+        <f>AA39-1</f>
+        <v>21</v>
+      </c>
+      <c r="AC39" s="45">
+        <f>AB39-1</f>
+        <v>20</v>
+      </c>
+      <c r="AD39" s="45">
+        <f>AC39-1</f>
+        <v>19</v>
+      </c>
+      <c r="AE39" s="45">
+        <f>AD39-1</f>
+        <v>18</v>
+      </c>
+      <c r="AF39" s="45">
+        <f>AE39-1</f>
+        <v>17</v>
+      </c>
+      <c r="AG39" s="45">
+        <f>AF39-1</f>
+        <v>16</v>
+      </c>
+      <c r="AH39" s="45">
+        <f>AG39-1</f>
+        <v>15</v>
+      </c>
+      <c r="AI39" s="45">
+        <f>AH39-1</f>
+        <v>14</v>
+      </c>
+      <c r="AJ39" s="45">
+        <f>AI39-1</f>
+        <v>13</v>
+      </c>
+      <c r="AK39" s="45">
+        <f>AJ39-1</f>
+        <v>12</v>
+      </c>
+      <c r="AL39" s="45">
+        <f>AK39-1</f>
+        <v>11</v>
+      </c>
+      <c r="AM39" s="45">
+        <f>AL39-1</f>
+        <v>10</v>
+      </c>
+      <c r="AN39" s="45">
+        <f>AM39-1</f>
+        <v>9</v>
+      </c>
+      <c r="AO39" s="45">
+        <f>AN39-1</f>
+        <v>8</v>
+      </c>
+      <c r="AP39" s="45">
+        <f>AO39-1</f>
+        <v>7</v>
+      </c>
+      <c r="AQ39" s="45">
+        <f>AP39-1</f>
+        <v>6</v>
+      </c>
+      <c r="AR39" s="45">
+        <f>AQ39-1</f>
+        <v>5</v>
+      </c>
+      <c r="AS39" s="45">
+        <f>AR39-1</f>
+        <v>4</v>
+      </c>
+      <c r="AT39" s="45">
+        <f>AS39-1</f>
+        <v>3</v>
+      </c>
+      <c r="AU39" s="45">
+        <f>AT39-1</f>
+        <v>2</v>
+      </c>
+      <c r="AV39" s="45">
+        <f>AU39-1</f>
+        <v>1</v>
+      </c>
+      <c r="AW39" s="45">
+        <f>AV39-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:49" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Q40" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="R40" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="S40" s="48"/>
+      <c r="T40" s="48"/>
+      <c r="U40" s="48"/>
+      <c r="V40" s="48"/>
+      <c r="W40" s="48"/>
+      <c r="X40" s="49"/>
+      <c r="Y40" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z40" s="48"/>
+      <c r="AA40" s="48"/>
+      <c r="AB40" s="48"/>
+      <c r="AC40" s="49"/>
+      <c r="AD40" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE40" s="48"/>
+      <c r="AF40" s="48"/>
+      <c r="AG40" s="48"/>
+      <c r="AH40" s="49"/>
+      <c r="AI40" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ40" s="48"/>
+      <c r="AK40" s="49"/>
+      <c r="AL40" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM40" s="48"/>
+      <c r="AN40" s="48"/>
+      <c r="AO40" s="48"/>
+      <c r="AP40" s="49"/>
+      <c r="AQ40" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR40" s="48"/>
+      <c r="AS40" s="48"/>
+      <c r="AT40" s="48"/>
+      <c r="AU40" s="48"/>
+      <c r="AV40" s="48"/>
+      <c r="AW40" s="49"/>
+    </row>
+    <row r="41" spans="1:49" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Q41" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="R41" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="Q39" s="45">
-        <v>31</v>
-      </c>
-      <c r="R39" s="45">
-        <v>30</v>
-      </c>
-      <c r="S39" s="45">
-        <v>29</v>
-      </c>
-      <c r="T39" s="45">
-        <f>S39-1</f>
-        <v>28</v>
-      </c>
-      <c r="U39" s="45">
-        <f t="shared" ref="U39:AV39" si="3">T39-1</f>
-        <v>27</v>
-      </c>
-      <c r="V39" s="45">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="W39" s="45">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="X39" s="45">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="Y39" s="45">
-        <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-      <c r="Z39" s="45">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="AA39" s="45">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="AB39" s="45">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="AC39" s="45">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="AD39" s="45">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="AE39" s="45">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-      <c r="AF39" s="45">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="AG39" s="45">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="AH39" s="45">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AI39" s="45">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="AJ39" s="45">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="AK39" s="45">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="AL39" s="45">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="AM39" s="45">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="AN39" s="45">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="AO39" s="45">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="AP39" s="45">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="AQ39" s="45">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="AR39" s="45">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="AS39" s="45">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="AT39" s="45">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AU39" s="45">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AV39" s="45">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:48" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="P40" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q40" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="R40" s="47"/>
-      <c r="S40" s="47"/>
-      <c r="T40" s="47"/>
-      <c r="U40" s="47"/>
-      <c r="V40" s="47"/>
-      <c r="W40" s="47"/>
-      <c r="X40" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y40" s="47"/>
-      <c r="Z40" s="47"/>
-      <c r="AA40" s="47"/>
-      <c r="AB40" s="47"/>
-      <c r="AC40" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD40" s="47"/>
-      <c r="AE40" s="47"/>
-      <c r="AF40" s="47"/>
-      <c r="AG40" s="47"/>
-      <c r="AH40" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI40" s="47"/>
-      <c r="AJ40" s="47"/>
-      <c r="AK40" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL40" s="47"/>
-      <c r="AM40" s="47"/>
-      <c r="AN40" s="47"/>
-      <c r="AO40" s="47"/>
-      <c r="AP40" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="AQ40" s="47"/>
-      <c r="AR40" s="47"/>
-      <c r="AS40" s="47"/>
-      <c r="AT40" s="47"/>
-      <c r="AU40" s="47"/>
-      <c r="AV40" s="47"/>
-    </row>
-    <row r="41" spans="1:48" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="P41" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q41" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="R41" s="47"/>
-      <c r="S41" s="47"/>
-      <c r="T41" s="47"/>
-      <c r="U41" s="47"/>
-      <c r="V41" s="47"/>
-      <c r="W41" s="47"/>
-      <c r="X41" s="47"/>
-      <c r="Y41" s="47"/>
-      <c r="Z41" s="47"/>
-      <c r="AA41" s="47"/>
-      <c r="AB41" s="47"/>
-      <c r="AC41" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD41" s="47"/>
-      <c r="AE41" s="47"/>
-      <c r="AF41" s="47"/>
-      <c r="AG41" s="47"/>
-      <c r="AH41" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI41" s="47"/>
-      <c r="AJ41" s="47"/>
-      <c r="AK41" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL41" s="47"/>
-      <c r="AM41" s="47"/>
-      <c r="AN41" s="47"/>
-      <c r="AO41" s="47"/>
-      <c r="AP41" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="AQ41" s="47"/>
-      <c r="AR41" s="47"/>
-      <c r="AS41" s="47"/>
-      <c r="AT41" s="47"/>
-      <c r="AU41" s="47"/>
-      <c r="AV41" s="47"/>
-    </row>
-    <row r="42" spans="1:48" s="36" customFormat="1" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="S41" s="48"/>
+      <c r="T41" s="48"/>
+      <c r="U41" s="48"/>
+      <c r="V41" s="48"/>
+      <c r="W41" s="48"/>
+      <c r="X41" s="48"/>
+      <c r="Y41" s="48"/>
+      <c r="Z41" s="48"/>
+      <c r="AA41" s="48"/>
+      <c r="AB41" s="48"/>
+      <c r="AC41" s="49"/>
+      <c r="AD41" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE41" s="48"/>
+      <c r="AF41" s="48"/>
+      <c r="AG41" s="48"/>
+      <c r="AH41" s="49"/>
+      <c r="AI41" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ41" s="48"/>
+      <c r="AK41" s="49"/>
+      <c r="AL41" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM41" s="48"/>
+      <c r="AN41" s="48"/>
+      <c r="AO41" s="48"/>
+      <c r="AP41" s="49"/>
+      <c r="AQ41" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR41" s="48"/>
+      <c r="AS41" s="48"/>
+      <c r="AT41" s="48"/>
+      <c r="AU41" s="48"/>
+      <c r="AV41" s="48"/>
+      <c r="AW41" s="49"/>
+    </row>
+    <row r="42" spans="1:49" s="36" customFormat="1" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="40"/>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
@@ -3324,231 +3517,231 @@
       <c r="M42" s="41"/>
       <c r="N42" s="41"/>
       <c r="O42" s="41"/>
-      <c r="P42" s="45" t="s">
+      <c r="Q42" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="Q42" s="47" t="s">
+      <c r="R42" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="S42" s="48"/>
+      <c r="T42" s="48"/>
+      <c r="U42" s="48"/>
+      <c r="V42" s="48"/>
+      <c r="W42" s="48"/>
+      <c r="X42" s="49"/>
+      <c r="Y42" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z42" s="48"/>
+      <c r="AA42" s="48"/>
+      <c r="AB42" s="48"/>
+      <c r="AC42" s="49"/>
+      <c r="AD42" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE42" s="48"/>
+      <c r="AF42" s="48"/>
+      <c r="AG42" s="48"/>
+      <c r="AH42" s="49"/>
+      <c r="AI42" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ42" s="48"/>
+      <c r="AK42" s="49"/>
+      <c r="AL42" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="AM42" s="48"/>
+      <c r="AN42" s="48"/>
+      <c r="AO42" s="48"/>
+      <c r="AP42" s="49"/>
+      <c r="AQ42" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR42" s="48"/>
+      <c r="AS42" s="48"/>
+      <c r="AT42" s="48"/>
+      <c r="AU42" s="48"/>
+      <c r="AV42" s="48"/>
+      <c r="AW42" s="49"/>
+    </row>
+    <row r="43" spans="1:49" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Q43" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="R43" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="S43" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="T43" s="48"/>
+      <c r="U43" s="48"/>
+      <c r="V43" s="48"/>
+      <c r="W43" s="48"/>
+      <c r="X43" s="49"/>
+      <c r="Y43" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z43" s="48"/>
+      <c r="AA43" s="48"/>
+      <c r="AB43" s="48"/>
+      <c r="AC43" s="49"/>
+      <c r="AD43" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE43" s="48"/>
+      <c r="AF43" s="48"/>
+      <c r="AG43" s="48"/>
+      <c r="AH43" s="49"/>
+      <c r="AI43" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ43" s="48"/>
+      <c r="AK43" s="49"/>
+      <c r="AL43" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM43" s="48"/>
+      <c r="AN43" s="48"/>
+      <c r="AO43" s="49"/>
+      <c r="AP43" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="AQ43" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR43" s="48"/>
+      <c r="AS43" s="48"/>
+      <c r="AT43" s="48"/>
+      <c r="AU43" s="48"/>
+      <c r="AV43" s="48"/>
+      <c r="AW43" s="49"/>
+    </row>
+    <row r="44" spans="1:49" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Q44" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="R44" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="S44" s="47" t="s">
         <v>162</v>
       </c>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="47"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y42" s="47"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="47"/>
-      <c r="AC42" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD42" s="47"/>
-      <c r="AE42" s="47"/>
-      <c r="AF42" s="47"/>
-      <c r="AG42" s="47"/>
-      <c r="AH42" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI42" s="47"/>
-      <c r="AJ42" s="47"/>
-      <c r="AK42" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="AL42" s="47"/>
-      <c r="AM42" s="47"/>
-      <c r="AN42" s="47"/>
-      <c r="AO42" s="47"/>
-      <c r="AP42" s="47" t="s">
+      <c r="T44" s="48"/>
+      <c r="U44" s="48"/>
+      <c r="V44" s="48"/>
+      <c r="W44" s="48"/>
+      <c r="X44" s="48"/>
+      <c r="Y44" s="48"/>
+      <c r="Z44" s="48"/>
+      <c r="AA44" s="48"/>
+      <c r="AB44" s="49"/>
+      <c r="AC44" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD44" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="AQ42" s="47"/>
-      <c r="AR42" s="47"/>
-      <c r="AS42" s="47"/>
-      <c r="AT42" s="47"/>
-      <c r="AU42" s="47"/>
-      <c r="AV42" s="47"/>
-    </row>
-    <row r="43" spans="1:48" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="P43" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q43" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="R43" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="47"/>
-      <c r="V43" s="47"/>
-      <c r="W43" s="47"/>
-      <c r="X43" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y43" s="47"/>
-      <c r="Z43" s="47"/>
-      <c r="AA43" s="47"/>
-      <c r="AB43" s="47"/>
-      <c r="AC43" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD43" s="47"/>
-      <c r="AE43" s="47"/>
-      <c r="AF43" s="47"/>
-      <c r="AG43" s="47"/>
-      <c r="AH43" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI43" s="47"/>
-      <c r="AJ43" s="47"/>
-      <c r="AK43" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL43" s="47"/>
-      <c r="AM43" s="47"/>
-      <c r="AN43" s="47"/>
-      <c r="AO43" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AP43" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="AQ43" s="47"/>
-      <c r="AR43" s="47"/>
-      <c r="AS43" s="47"/>
-      <c r="AT43" s="47"/>
-      <c r="AU43" s="47"/>
-      <c r="AV43" s="47"/>
-    </row>
-    <row r="44" spans="1:48" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="P44" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q44" s="46" t="s">
+      <c r="AE44" s="48"/>
+      <c r="AF44" s="48"/>
+      <c r="AG44" s="48"/>
+      <c r="AH44" s="48"/>
+      <c r="AI44" s="48"/>
+      <c r="AJ44" s="48"/>
+      <c r="AK44" s="49"/>
+      <c r="AL44" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM44" s="48"/>
+      <c r="AN44" s="48"/>
+      <c r="AO44" s="48"/>
+      <c r="AP44" s="49"/>
+      <c r="AQ44" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="R44" s="47" t="s">
+      <c r="AR44" s="48"/>
+      <c r="AS44" s="48"/>
+      <c r="AT44" s="48"/>
+      <c r="AU44" s="48"/>
+      <c r="AV44" s="48"/>
+      <c r="AW44" s="49"/>
+    </row>
+    <row r="45" spans="1:49" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="Q45" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="R45" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="S45" s="48"/>
+      <c r="T45" s="48"/>
+      <c r="U45" s="48"/>
+      <c r="V45" s="48"/>
+      <c r="W45" s="48"/>
+      <c r="X45" s="48"/>
+      <c r="Y45" s="48"/>
+      <c r="Z45" s="48"/>
+      <c r="AA45" s="48"/>
+      <c r="AB45" s="48"/>
+      <c r="AC45" s="48"/>
+      <c r="AD45" s="48"/>
+      <c r="AE45" s="48"/>
+      <c r="AF45" s="48"/>
+      <c r="AG45" s="48"/>
+      <c r="AH45" s="48"/>
+      <c r="AI45" s="48"/>
+      <c r="AJ45" s="48"/>
+      <c r="AK45" s="49"/>
+      <c r="AL45" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="47"/>
-      <c r="V44" s="47"/>
-      <c r="W44" s="47"/>
-      <c r="X44" s="47"/>
-      <c r="Y44" s="47"/>
-      <c r="Z44" s="47"/>
-      <c r="AA44" s="47"/>
-      <c r="AB44" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AC44" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="AD44" s="47"/>
-      <c r="AE44" s="47"/>
-      <c r="AF44" s="47"/>
-      <c r="AG44" s="47"/>
-      <c r="AH44" s="47"/>
-      <c r="AI44" s="47"/>
-      <c r="AJ44" s="47"/>
-      <c r="AK44" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL44" s="47"/>
-      <c r="AM44" s="47"/>
-      <c r="AN44" s="47"/>
-      <c r="AO44" s="47"/>
-      <c r="AP44" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="AQ44" s="47"/>
-      <c r="AR44" s="47"/>
-      <c r="AS44" s="47"/>
-      <c r="AT44" s="47"/>
-      <c r="AU44" s="47"/>
-      <c r="AV44" s="47"/>
-    </row>
-    <row r="45" spans="1:48" ht="39.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="P45" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q45" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
-      <c r="W45" s="47"/>
-      <c r="X45" s="47"/>
-      <c r="Y45" s="47"/>
-      <c r="Z45" s="47"/>
-      <c r="AA45" s="47"/>
-      <c r="AB45" s="47"/>
-      <c r="AC45" s="47"/>
-      <c r="AD45" s="47"/>
-      <c r="AE45" s="47"/>
-      <c r="AF45" s="47"/>
-      <c r="AG45" s="47"/>
-      <c r="AH45" s="47"/>
-      <c r="AI45" s="47"/>
-      <c r="AJ45" s="47"/>
-      <c r="AK45" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL45" s="47"/>
-      <c r="AM45" s="47"/>
-      <c r="AN45" s="47"/>
-      <c r="AO45" s="47"/>
-      <c r="AP45" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="AQ45" s="47"/>
-      <c r="AR45" s="47"/>
-      <c r="AS45" s="47"/>
-      <c r="AT45" s="47"/>
-      <c r="AU45" s="47"/>
-      <c r="AV45" s="47"/>
+      <c r="AM45" s="48"/>
+      <c r="AN45" s="48"/>
+      <c r="AO45" s="48"/>
+      <c r="AP45" s="49"/>
+      <c r="AQ45" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR45" s="48"/>
+      <c r="AS45" s="48"/>
+      <c r="AT45" s="48"/>
+      <c r="AU45" s="48"/>
+      <c r="AV45" s="48"/>
+      <c r="AW45" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="Q45:AJ45"/>
-    <mergeCell ref="X40:AB40"/>
-    <mergeCell ref="X42:AB42"/>
-    <mergeCell ref="X43:AB43"/>
-    <mergeCell ref="R43:W43"/>
-    <mergeCell ref="AC40:AG40"/>
-    <mergeCell ref="AC41:AG41"/>
-    <mergeCell ref="AC42:AG42"/>
-    <mergeCell ref="AC43:AG43"/>
-    <mergeCell ref="Q40:W40"/>
-    <mergeCell ref="Q41:AB41"/>
-    <mergeCell ref="Q42:W42"/>
-    <mergeCell ref="AC44:AJ44"/>
-    <mergeCell ref="R44:AA44"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AK40:AO40"/>
-    <mergeCell ref="AK41:AO41"/>
-    <mergeCell ref="AK42:AO42"/>
-    <mergeCell ref="AK45:AO45"/>
-    <mergeCell ref="AK43:AN43"/>
-    <mergeCell ref="AP40:AV40"/>
-    <mergeCell ref="AP41:AV41"/>
-    <mergeCell ref="AP42:AV42"/>
-    <mergeCell ref="AP43:AV43"/>
-    <mergeCell ref="AP45:AV45"/>
-    <mergeCell ref="AP44:AV44"/>
-    <mergeCell ref="AK44:AO44"/>
+    <mergeCell ref="R42:X42"/>
+    <mergeCell ref="S43:X43"/>
+    <mergeCell ref="S44:AB44"/>
+    <mergeCell ref="R45:AK45"/>
+    <mergeCell ref="AD44:AK44"/>
+    <mergeCell ref="AD43:AH43"/>
+    <mergeCell ref="AD42:AH42"/>
+    <mergeCell ref="Y42:AC42"/>
+    <mergeCell ref="Y43:AC43"/>
+    <mergeCell ref="R40:X40"/>
+    <mergeCell ref="Y40:AC40"/>
+    <mergeCell ref="AD40:AH40"/>
+    <mergeCell ref="AI40:AK40"/>
+    <mergeCell ref="AI41:AK41"/>
+    <mergeCell ref="R41:AC41"/>
+    <mergeCell ref="AD41:AH41"/>
+    <mergeCell ref="AQ44:AW44"/>
+    <mergeCell ref="AQ45:AW45"/>
+    <mergeCell ref="AL40:AP40"/>
+    <mergeCell ref="AL41:AP41"/>
+    <mergeCell ref="AL42:AP42"/>
+    <mergeCell ref="AL43:AO43"/>
+    <mergeCell ref="AL44:AP44"/>
+    <mergeCell ref="AL45:AP45"/>
+    <mergeCell ref="AQ40:AW40"/>
+    <mergeCell ref="AQ41:AW41"/>
+    <mergeCell ref="AQ42:AW42"/>
+    <mergeCell ref="AQ43:AW43"/>
+    <mergeCell ref="AI43:AK43"/>
+    <mergeCell ref="AI42:AK42"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3557,8 +3750,5 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="38" max="16383" man="1"/>
   </rowBreaks>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="15" max="1048575" man="1"/>
-  </colBreaks>
 </worksheet>
 </file>